--- a/examples/17_kitchen_sink/sink_config.xlsx
+++ b/examples/17_kitchen_sink/sink_config.xlsx
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>col:C</t>
+          <t>expr:{order_date}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2409,11 +2409,6 @@
       <c r="H25" t="n">
         <v>24</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>%m/%d/%Y</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>year_month</t>
@@ -2421,7 +2416,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>date cast + year_month script</t>
+          <t>expr refs computed date + year_month</t>
         </is>
       </c>
     </row>

--- a/examples/17_kitchen_sink/sink_config.xlsx
+++ b/examples/17_kitchen_sink/sink_config.xlsx
@@ -384,10 +384,14 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.
-Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;
+Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...
 Example: col:A</t>
       </text>
     </comment>
@@ -1224,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2818,12 +2822,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>col:A</t>
+          <t>map:Title||Date||Currency||Region||Order Count</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>field_name</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2844,14 +2848,9 @@
       <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>the key/label</t>
+          <t>map: user-provided labels</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2862,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>col:B</t>
+          <t>col:A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2878,7 +2877,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2896,7 +2895,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>the value, kept as text</t>
+          <t>the key/label from source</t>
         </is>
       </c>
     </row>
@@ -2908,17 +2907,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>fn:now</t>
+          <t>col:B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>captured_at</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2934,54 +2933,54 @@
       <c r="H36" t="n">
         <v>3</v>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>when this was loaded</t>
+          <t>the value, kept as text</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>archive</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>col:A</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Old ID</t>
+          <t>fn:now</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>old_id</t>
+          <t>captured_at</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>inactive — skipped entirely</t>
+          <t>when this was loaded</t>
         </is>
       </c>
     </row>
@@ -2993,38 +2992,83 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>col:A</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Old ID</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>old_id</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inactive — skipped entirely</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>col:B</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Old Data</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>old_data</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>2</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>inactive — skipped entirely</t>
         </is>
@@ -3721,6 +3765,10 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.</t>
@@ -3728,7 +3776,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;</t>
+          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
